--- a/input/New_Vehicle_Delivery_Experience_30_Days.xlsx
+++ b/input/New_Vehicle_Delivery_Experience_30_Days.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OMEN\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Sales Audit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B39A582-A479-4E15-8690-1B0D4606679D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEE0A74F-5DC3-458F-9405-8C164113ED64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>Zone</t>
   </si>
@@ -64,52 +64,55 @@
     <t>UNNATI MOTORS, A DIVISION OF MICROPARK LOGISTICS PRIVATE LIMITED</t>
   </si>
   <si>
-    <t>HINDUSTAN COLONY</t>
-  </si>
-  <si>
-    <t>VDN27I000085</t>
-  </si>
-  <si>
-    <t>CF2700151939</t>
-  </si>
-  <si>
-    <t>XUV3XO</t>
+    <t>NAGPUR_KAMPTHEE ROAD</t>
+  </si>
+  <si>
+    <t>VDN27A000596</t>
+  </si>
+  <si>
+    <t>CF2700189011</t>
+  </si>
+  <si>
+    <t>XUV 7XO</t>
+  </si>
+  <si>
+    <t>Satisfied</t>
+  </si>
+  <si>
+    <t>"Worst experience with Unnati Mahindra! Third-class service, zero responsiveness, and pathetic behavior toward customers."</t>
+  </si>
+  <si>
+    <t>KARTIK NARAYAN HATWAR</t>
+  </si>
+  <si>
+    <t>13FL6733</t>
+  </si>
+  <si>
+    <t>UNNATI MOTORS</t>
+  </si>
+  <si>
+    <t>MANJHARI_SH</t>
+  </si>
+  <si>
+    <t>VDN27N000204</t>
+  </si>
+  <si>
+    <t>15865056</t>
+  </si>
+  <si>
+    <t>SCORPIO-N</t>
   </si>
   <si>
     <t>Somewhat satisfied</t>
   </si>
   <si>
-    <t>Hopeless delivery experience</t>
-  </si>
-  <si>
-    <t>KARTIK NAMDEVRAO SHELKE</t>
-  </si>
-  <si>
-    <t>13NT3475</t>
-  </si>
-  <si>
-    <t>UNNATI MOTORS</t>
-  </si>
-  <si>
-    <t>WARJE_SZS</t>
-  </si>
-  <si>
-    <t>VDN27O000171</t>
-  </si>
-  <si>
-    <t>CF2700176978</t>
-  </si>
-  <si>
-    <t>Very dissatisfied</t>
-  </si>
-  <si>
-    <t>Bad delivery experience,  so many scratches on new car.</t>
-  </si>
-  <si>
-    <t>YADNESHWAR R ZORE</t>
-  </si>
-  <si>
-    <t>13RX2429</t>
+    <t>The delivery process was not smooth ..many calls and reminders had to be made for the delivery even after full payment. The accessories have still not been provided completely after full payment for accessories. Bad Customer service.</t>
+  </si>
+  <si>
+    <t>RUTIK BALASAHEB KUNJIR</t>
+  </si>
+  <si>
+    <t>13QW2364</t>
   </si>
 </sst>
 </file>
@@ -574,19 +577,19 @@
         <v>25</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
